--- a/reports/module-data-integration-audit/2026-07-27/CANONICAL_PROMOTION_MATRIX.xlsx
+++ b/reports/module-data-integration-audit/2026-07-27/CANONICAL_PROMOTION_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotion" sheetId="1" r:id="R47759f2261de44b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotion" sheetId="1" r:id="R765fd3e5e30349a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,13 +346,13 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>Moves</x:v>
+        <x:v>Source</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>public.approved</x:v>
+        <x:v>public.evidence</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>knowledge.application</x:v>
+        <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -364,21 +364,19 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G2" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H2" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H2" s="5" t="str"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>Moves</x:v>
+        <x:v>Source</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>public.move_artifact_review_decisions</x:v>
+        <x:v>public.home_knowledge_evidence_sources</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>knowledge.program</x:v>
+        <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -390,19 +388,19 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G3" s="5" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="H3" s="5" t="str"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>Moves</x:v>
+        <x:v>Source</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>public.move_artifacts</x:v>
+        <x:v>public.source_artifact_chunks</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>knowledge.program</x:v>
+        <x:v>knowledge.evidence_chunk</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -420,13 +418,13 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>Moves</x:v>
+        <x:v>Source</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>public.move_template_artifacts</x:v>
+        <x:v>public.source_artifact_facts</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>knowledge.program</x:v>
+        <x:v>knowledge.fact</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -438,19 +436,19 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H5" s="5" t="str"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>Moves</x:v>
+        <x:v>Source</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>public.move_template_gates</x:v>
+        <x:v>public.source_contract_evidence_manifests</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>knowledge.program</x:v>
+        <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -462,19 +460,19 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G6" s="5" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H6" s="5" t="str"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>Moves</x:v>
+        <x:v>Source</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>public.program_evidence_reviews</x:v>
+        <x:v>public.source_contract_evidence_metrics</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>knowledge.program</x:v>
+        <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -495,10 +493,10 @@
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>public.artifact</x:v>
+        <x:v>public.source_contract_evidence_rows</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>knowledge.evidence</x:v>
+        <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -510,18 +508,16 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G8" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H8" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H8" s="5" t="str"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>public.contract</x:v>
+        <x:v>public.source_contract_optimization_findings</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
         <x:v>knowledge.contract</x:v>
@@ -536,18 +532,16 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G9" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H9" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="str"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="5" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>public.CONTRACT_TERMS_V1</x:v>
+        <x:v>public.source_contract_optimization_levers</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
         <x:v>knowledge.contract</x:v>
@@ -562,18 +556,16 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G10" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H10" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="str"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="5" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>public.contracting</x:v>
+        <x:v>public.source_contract_optimization_profiles</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
         <x:v>knowledge.contract</x:v>
@@ -590,19 +582,17 @@
       <x:c r="G11" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H11" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
+      <x:c r="H11" s="5" t="str"/>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="5" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B12" s="5" t="str">
-        <x:v>public.contractor</x:v>
+        <x:v>public.source_event_facts</x:v>
       </x:c>
       <x:c r="C12" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.fact</x:v>
       </x:c>
       <x:c r="D12" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -616,19 +606,17 @@
       <x:c r="G12" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H12" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
+      <x:c r="H12" s="5" t="str"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="5" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>public.contractual</x:v>
+        <x:v>public.source_meeting_outcomes</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.metric</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -642,19 +630,17 @@
       <x:c r="G13" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H13" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
+      <x:c r="H13" s="5" t="str"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="5" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>public.enterprise_context_source_files</x:v>
+        <x:v>public.source_value_chain</x:v>
       </x:c>
       <x:c r="C14" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>knowledge.metric</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -666,7 +652,7 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G14" s="5" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="H14" s="5" t="str"/>
     </x:row>
@@ -675,10 +661,10 @@
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>public.enterprise_context_sources</x:v>
+        <x:v>public.source_value_levers</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>knowledge.metric</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -690,7 +676,7 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G15" s="5" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H15" s="5" t="str"/>
     </x:row>
@@ -699,10 +685,10 @@
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>public.evidence</x:v>
+        <x:v>public.source_value_lines</x:v>
       </x:c>
       <x:c r="C16" s="5" t="str">
-        <x:v>knowledge.evidence</x:v>
+        <x:v>knowledge.metric</x:v>
       </x:c>
       <x:c r="D16" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -714,7 +700,7 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G16" s="5" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="H16" s="5" t="str"/>
     </x:row>
@@ -723,10 +709,10 @@
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>public.facts</x:v>
+        <x:v>public.source_value_states</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>knowledge.metric</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -740,19 +726,17 @@
       <x:c r="G17" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H17" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
+      <x:c r="H17" s="5" t="str"/>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="5" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>public.outcome</x:v>
+        <x:v>public.source_vendor_commitments</x:v>
       </x:c>
       <x:c r="C18" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.vendor</x:v>
       </x:c>
       <x:c r="D18" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -764,21 +748,19 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G18" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H18" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H18" s="5" t="str"/>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="5" t="str">
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>public.source_artifact_acceptances</x:v>
+        <x:v>public.source_vendor_proposal_facts</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
-        <x:v>knowledge.evidence</x:v>
+        <x:v>knowledge.vendor</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -799,10 +781,10 @@
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
-        <x:v>public.source_artifact_chunks</x:v>
+        <x:v>public.vendor_contracts</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
-        <x:v>knowledge.evidence</x:v>
+        <x:v>knowledge.vendor</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -814,19 +796,21 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G20" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H20" s="5" t="str"/>
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="H20" s="5" t="str">
+        <x:v>Lineage field not found statically</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B21" s="5" t="str">
-        <x:v>public.source_artifact_facts</x:v>
+        <x:v>cio_tower.measures</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
-        <x:v>knowledge.evidence</x:v>
+        <x:v>knowledge.metric_definition</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -838,19 +822,19 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G21" s="5" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="H21" s="5" t="str"/>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B22" s="5" t="str">
-        <x:v>public.source_artifacts</x:v>
+        <x:v>cio_tower.tool_identity_aliases</x:v>
       </x:c>
       <x:c r="C22" s="5" t="str">
-        <x:v>knowledge.evidence</x:v>
+        <x:v>to_be_mapped</x:v>
       </x:c>
       <x:c r="D22" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -862,19 +846,19 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G22" s="5" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="H22" s="5" t="str"/>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B23" s="5" t="str">
-        <x:v>public.source_contract_evidence_manifests</x:v>
+        <x:v>public.ai_control_actions</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -892,13 +876,13 @@
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
-        <x:v>public.source_contract_evidence_metrics</x:v>
+        <x:v>public.ai_control_agent_outcomes</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.metric</x:v>
       </x:c>
       <x:c r="D24" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -916,13 +900,13 @@
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>public.source_contract_evidence_rows</x:v>
+        <x:v>public.ai_control_benefit_realization</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -940,13 +924,13 @@
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B26" s="5" t="str">
-        <x:v>public.source_contract_optimization_findings</x:v>
+        <x:v>public.ai_control_context_facts</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="D26" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -964,13 +948,13 @@
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B27" s="5" t="str">
-        <x:v>public.source_contract_optimization_levers</x:v>
+        <x:v>public.ai_control_context_relationships</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="D27" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -984,17 +968,19 @@
       <x:c r="G27" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="H27" s="5" t="str"/>
+      <x:c r="H27" s="5" t="str">
+        <x:v>Lineage field not found statically</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B28" s="5" t="str">
-        <x:v>public.source_contract_optimization_profiles</x:v>
+        <x:v>public.ai_control_dora_metrics</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.metric</x:v>
       </x:c>
       <x:c r="D28" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -1006,19 +992,19 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G28" s="5" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H28" s="5" t="str"/>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B29" s="5" t="str">
-        <x:v>public.source_event_artifact_states</x:v>
+        <x:v>public.ai_control_evidence_items</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
-        <x:v>knowledge.evidence</x:v>
+        <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -1036,13 +1022,13 @@
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B30" s="5" t="str">
-        <x:v>public.source_event_facts</x:v>
+        <x:v>public.ai_control_initiatives</x:v>
       </x:c>
       <x:c r="C30" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="D30" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -1054,19 +1040,19 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G30" s="5" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H30" s="5" t="str"/>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B31" s="5" t="str">
-        <x:v>public.source_event_gate_criterion_states</x:v>
+        <x:v>public.ai_control_persona_productivity</x:v>
       </x:c>
       <x:c r="C31" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="D31" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -1084,13 +1070,13 @@
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B32" s="5" t="str">
-        <x:v>public.source_meeting_outcomes</x:v>
+        <x:v>public.ai_control_risk_governance</x:v>
       </x:c>
       <x:c r="C32" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="D32" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -1102,19 +1088,19 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G32" s="5" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H32" s="5" t="str"/>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B33" s="5" t="str">
-        <x:v>public.source_reasoning_envelopes</x:v>
+        <x:v>public.ai_control_spend_contracts</x:v>
       </x:c>
       <x:c r="C33" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="D33" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -1132,13 +1118,13 @@
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B34" s="5" t="str">
-        <x:v>public.source_value_levers</x:v>
+        <x:v>public.ai_control_tool_usage_monthly</x:v>
       </x:c>
       <x:c r="C34" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="D34" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -1156,13 +1142,13 @@
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B35" s="5" t="str">
-        <x:v>public.source_value_lines</x:v>
+        <x:v>public.application_portfolio</x:v>
       </x:c>
       <x:c r="C35" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.application</x:v>
       </x:c>
       <x:c r="D35" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -1176,17 +1162,19 @@
       <x:c r="G35" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H35" s="5" t="str"/>
+      <x:c r="H35" s="5" t="str">
+        <x:v>Lineage field not found statically</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B36" s="5" t="str">
-        <x:v>public.source_value_states</x:v>
+        <x:v>public.enterprise_context_records</x:v>
       </x:c>
       <x:c r="C36" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>to_be_mapped</x:v>
       </x:c>
       <x:c r="D36" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -1198,19 +1186,19 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G36" s="5" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H36" s="5" t="str"/>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B37" s="5" t="str">
-        <x:v>public.source_vendor_commitments</x:v>
+        <x:v>public.tower_cmdb_cis</x:v>
       </x:c>
       <x:c r="C37" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
+        <x:v>knowledge.application</x:v>
       </x:c>
       <x:c r="D37" s="5" t="str">
         <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
@@ -1222,16 +1210,16 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G37" s="5" t="str">
-        <x:v>High</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="H37" s="5" t="str"/>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="5" t="str">
-        <x:v>Source</x:v>
+        <x:v>Tower</x:v>
       </x:c>
       <x:c r="B38" s="5" t="str">
-        <x:v>public.source_vendor_proposal_fact_reviews</x:v>
+        <x:v>public.tower_read_model_vendors</x:v>
       </x:c>
       <x:c r="C38" s="5" t="str">
         <x:v>knowledge.vendor</x:v>
@@ -1246,775 +1234,33 @@
         <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="G38" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H38" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H38" s="5" t="str"/>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
-      <x:c r="A39" s="5" t="str">
-        <x:v>Source</x:v>
-      </x:c>
-      <x:c r="B39" s="5" t="str">
-        <x:v>public.source_vendor_proposal_facts</x:v>
-      </x:c>
-      <x:c r="C39" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="D39" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E39" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F39" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G39" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H39" s="5" t="str"/>
-    </x:row>
-    <x:row r="40" ht="15" hidden="0" customHeight="1">
-      <x:c r="A40" s="5" t="str">
-        <x:v>Source</x:v>
-      </x:c>
-      <x:c r="B40" s="5" t="str">
-        <x:v>public.vendor</x:v>
-      </x:c>
-      <x:c r="C40" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="D40" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E40" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F40" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G40" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H40" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="15" hidden="0" customHeight="1">
-      <x:c r="A41" s="5" t="str">
-        <x:v>Source</x:v>
-      </x:c>
-      <x:c r="B41" s="5" t="str">
-        <x:v>public.Vendor</x:v>
-      </x:c>
-      <x:c r="C41" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="D41" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E41" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F41" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G41" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H41" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="15" hidden="0" customHeight="1">
-      <x:c r="A42" s="5" t="str">
-        <x:v>Source</x:v>
-      </x:c>
-      <x:c r="B42" s="5" t="str">
-        <x:v>public.vendor_comparison</x:v>
-      </x:c>
-      <x:c r="C42" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="D42" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E42" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F42" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G42" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H42" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="15" hidden="0" customHeight="1">
-      <x:c r="A43" s="5" t="str">
-        <x:v>Source</x:v>
-      </x:c>
-      <x:c r="B43" s="5" t="str">
-        <x:v>public.vendor_contracts</x:v>
-      </x:c>
-      <x:c r="C43" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="D43" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E43" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F43" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G43" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H43" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="15" hidden="0" customHeight="1">
-      <x:c r="A44" s="5" t="str">
-        <x:v>Source</x:v>
-      </x:c>
-      <x:c r="B44" s="5" t="str">
-        <x:v>public.vendors</x:v>
-      </x:c>
-      <x:c r="C44" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="D44" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E44" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F44" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G44" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H44" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="15" hidden="0" customHeight="1">
-      <x:c r="A45" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B45" s="5" t="str">
-        <x:v>cio_tower.facts</x:v>
-      </x:c>
-      <x:c r="C45" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="D45" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E45" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F45" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G45" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H45" s="5" t="str"/>
-    </x:row>
-    <x:row r="46" ht="15" hidden="0" customHeight="1">
-      <x:c r="A46" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B46" s="5" t="str">
-        <x:v>cio_tower.question_contracts</x:v>
-      </x:c>
-      <x:c r="C46" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
-      </x:c>
-      <x:c r="D46" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E46" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F46" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G46" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H46" s="5" t="str"/>
-    </x:row>
-    <x:row r="47" ht="15" hidden="0" customHeight="1">
-      <x:c r="A47" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B47" s="5" t="str">
-        <x:v>cio_tower.tool_identity_aliases</x:v>
-      </x:c>
-      <x:c r="C47" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="D47" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E47" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F47" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G47" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H47" s="5" t="str"/>
-    </x:row>
-    <x:row r="48" ht="15" hidden="0" customHeight="1">
-      <x:c r="A48" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B48" s="5" t="str">
-        <x:v>intelligence_v7.active_tenant_contract_versions</x:v>
-      </x:c>
-      <x:c r="C48" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
-      </x:c>
-      <x:c r="D48" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E48" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F48" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G48" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H48" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="15" hidden="0" customHeight="1">
-      <x:c r="A49" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B49" s="5" t="str">
-        <x:v>public.Accepted</x:v>
-      </x:c>
-      <x:c r="C49" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="D49" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E49" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F49" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G49" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H49" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="15" hidden="0" customHeight="1">
-      <x:c r="A50" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B50" s="5" t="str">
-        <x:v>public.ai_control_actions</x:v>
-      </x:c>
-      <x:c r="C50" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="D50" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E50" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F50" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G50" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H50" s="5" t="str"/>
-    </x:row>
-    <x:row r="51" ht="15" hidden="0" customHeight="1">
-      <x:c r="A51" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B51" s="5" t="str">
-        <x:v>public.ai_control_agent_outcomes</x:v>
-      </x:c>
-      <x:c r="C51" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
-      </x:c>
-      <x:c r="D51" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E51" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F51" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G51" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H51" s="5" t="str"/>
-    </x:row>
-    <x:row r="52" ht="15" hidden="0" customHeight="1">
-      <x:c r="A52" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B52" s="5" t="str">
-        <x:v>public.ai_control_atlas_context_packs</x:v>
-      </x:c>
-      <x:c r="C52" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="D52" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E52" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F52" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G52" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H52" s="5" t="str"/>
-    </x:row>
-    <x:row r="53" ht="15" hidden="0" customHeight="1">
-      <x:c r="A53" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B53" s="5" t="str">
-        <x:v>public.ai_control_benefit_realization</x:v>
-      </x:c>
-      <x:c r="C53" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="D53" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E53" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F53" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G53" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H53" s="5" t="str"/>
-    </x:row>
-    <x:row r="54" ht="15" hidden="0" customHeight="1">
-      <x:c r="A54" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B54" s="5" t="str">
-        <x:v>public.ai_control_context_facts</x:v>
-      </x:c>
-      <x:c r="C54" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="D54" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E54" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F54" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G54" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H54" s="5" t="str"/>
-    </x:row>
-    <x:row r="55" ht="15" hidden="0" customHeight="1">
-      <x:c r="A55" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B55" s="5" t="str">
-        <x:v>public.ai_control_dora_metrics</x:v>
-      </x:c>
-      <x:c r="C55" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
-      </x:c>
-      <x:c r="D55" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E55" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F55" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G55" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H55" s="5" t="str"/>
-    </x:row>
-    <x:row r="56" ht="15" hidden="0" customHeight="1">
-      <x:c r="A56" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B56" s="5" t="str">
-        <x:v>public.ai_control_evidence_items</x:v>
-      </x:c>
-      <x:c r="C56" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="D56" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E56" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F56" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G56" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H56" s="5" t="str"/>
-    </x:row>
-    <x:row r="57" ht="15" hidden="0" customHeight="1">
-      <x:c r="A57" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B57" s="5" t="str">
-        <x:v>public.ai_control_persona_productivity</x:v>
-      </x:c>
-      <x:c r="C57" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="D57" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E57" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F57" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G57" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H57" s="5" t="str"/>
-    </x:row>
-    <x:row r="58" ht="15" hidden="0" customHeight="1">
-      <x:c r="A58" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B58" s="5" t="str">
-        <x:v>public.ai_control_risk_governance</x:v>
-      </x:c>
-      <x:c r="C58" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="D58" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E58" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F58" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G58" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H58" s="5" t="str"/>
-    </x:row>
-    <x:row r="59" ht="15" hidden="0" customHeight="1">
-      <x:c r="A59" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B59" s="5" t="str">
-        <x:v>public.ai_control_spend_contracts</x:v>
-      </x:c>
-      <x:c r="C59" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
-      </x:c>
-      <x:c r="D59" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E59" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F59" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G59" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H59" s="5" t="str"/>
-    </x:row>
-    <x:row r="60" ht="15" hidden="0" customHeight="1">
-      <x:c r="A60" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B60" s="5" t="str">
-        <x:v>public.ai_control_tool_usage_monthly</x:v>
-      </x:c>
-      <x:c r="C60" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="D60" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E60" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F60" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G60" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H60" s="5" t="str"/>
-    </x:row>
-    <x:row r="61" ht="15" hidden="0" customHeight="1">
-      <x:c r="A61" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B61" s="5" t="str">
-        <x:v>public.artifacts</x:v>
-      </x:c>
-      <x:c r="C61" s="5" t="str">
-        <x:v>knowledge.evidence</x:v>
-      </x:c>
-      <x:c r="D61" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E61" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F61" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G61" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H61" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="15" hidden="0" customHeight="1">
-      <x:c r="A62" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B62" s="5" t="str">
-        <x:v>public.discovery_instruments</x:v>
-      </x:c>
-      <x:c r="C62" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="D62" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E62" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F62" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G62" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H62" s="5" t="str"/>
-    </x:row>
-    <x:row r="63" ht="15" hidden="0" customHeight="1">
-      <x:c r="A63" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B63" s="5" t="str">
-        <x:v>public.enterprise_context_records</x:v>
-      </x:c>
-      <x:c r="C63" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="D63" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E63" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F63" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G63" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H63" s="5" t="str"/>
-    </x:row>
-    <x:row r="64" ht="15" hidden="0" customHeight="1">
-      <x:c r="A64" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B64" s="5" t="str">
-        <x:v>public.metrics</x:v>
-      </x:c>
-      <x:c r="C64" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
-      </x:c>
-      <x:c r="D64" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E64" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F64" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G64" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H64" s="5" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="15" hidden="0" customHeight="1">
-      <x:c r="A65" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B65" s="5" t="str">
-        <x:v>public.tower_dora_metrics</x:v>
-      </x:c>
-      <x:c r="C65" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
-      </x:c>
-      <x:c r="D65" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E65" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F65" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G65" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H65" s="5" t="str"/>
-    </x:row>
-    <x:row r="66" ht="15" hidden="0" customHeight="1">
-      <x:c r="A66" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B66" s="5" t="str">
-        <x:v>public.tower_read_model_initiatives</x:v>
-      </x:c>
-      <x:c r="C66" s="5" t="str">
+      <x:c r="A39" s="6" t="str">
+        <x:v>Tower</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>public.use_cases</x:v>
+      </x:c>
+      <x:c r="C39" s="6" t="str">
         <x:v>knowledge.program</x:v>
       </x:c>
-      <x:c r="D66" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E66" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F66" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G66" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H66" s="5" t="str"/>
-    </x:row>
-    <x:row r="67" ht="15" hidden="0" customHeight="1">
-      <x:c r="A67" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B67" s="5" t="str">
-        <x:v>public.tower_read_model_vendors</x:v>
-      </x:c>
-      <x:c r="C67" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="D67" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E67" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F67" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G67" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H67" s="5" t="str"/>
-    </x:row>
-    <x:row r="68" ht="15" hidden="0" customHeight="1">
-      <x:c r="A68" s="5" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B68" s="5" t="str">
-        <x:v>public.tower_vendor_spend</x:v>
-      </x:c>
-      <x:c r="C68" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="D68" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E68" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F68" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G68" s="5" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H68" s="5" t="str"/>
-    </x:row>
-    <x:row r="69" ht="15" hidden="0" customHeight="1">
-      <x:c r="A69" s="6" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="B69" s="6" t="str">
-        <x:v>vendors.renewal_date</x:v>
-      </x:c>
-      <x:c r="C69" s="6" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="D69" s="6" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
-      </x:c>
-      <x:c r="E69" s="6" t="str">
-        <x:v>governance.object_identity_map</x:v>
-      </x:c>
-      <x:c r="F69" s="6" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
-      </x:c>
-      <x:c r="G69" s="6" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="H69" s="6" t="str">
-        <x:v>Lineage field not found statically</x:v>
-      </x:c>
+      <x:c r="D39" s="6" t="str">
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+      </x:c>
+      <x:c r="E39" s="6" t="str">
+        <x:v>governance.object_identity_map</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="G39" s="6" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="H39" s="6" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reports/module-data-integration-audit/2026-07-27/CANONICAL_PROMOTION_MATRIX.xlsx
+++ b/reports/module-data-integration-audit/2026-07-27/CANONICAL_PROMOTION_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotion" sheetId="1" r:id="R765fd3e5e30349a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotion" sheetId="1" r:id="R4e5217e0ef5e4237"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/reports/module-data-integration-audit/2026-07-27/CANONICAL_PROMOTION_MATRIX.xlsx
+++ b/reports/module-data-integration-audit/2026-07-27/CANONICAL_PROMOTION_MATRIX.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotion" sheetId="1" r:id="R4e5217e0ef5e4237"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotion" sheetId="1" r:id="Re96849bccc4544fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -310,12 +310,13 @@
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="21" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="39" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -326,21 +327,24 @@
         <x:v>schema_table</x:v>
       </x:c>
       <x:c r="C1" s="9" t="str">
-        <x:v>canonical_equivalent</x:v>
+        <x:v>provisional_canonical_object_family</x:v>
       </x:c>
       <x:c r="D1" s="9" t="str">
+        <x:v>mapping_confidence</x:v>
+      </x:c>
+      <x:c r="E1" s="9" t="str">
         <x:v>promotion_trigger</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>required_crosswalk</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>lineage_required</x:v>
       </x:c>
-      <x:c r="G1" s="9" t="str">
+      <x:c r="H1" s="9" t="str">
         <x:v>complexity</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="str">
+      <x:c r="I1" s="9" t="str">
         <x:v>blocker</x:v>
       </x:c>
     </x:row>
@@ -355,18 +359,21 @@
         <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E2" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F2" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G2" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H2" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H2" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I2" s="5" t="str"/>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
@@ -379,18 +386,21 @@
         <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F3" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G3" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H3" s="5" t="str"/>
+      <x:c r="I3" s="5" t="str"/>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
@@ -403,18 +413,21 @@
         <x:v>knowledge.evidence_chunk</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F4" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G4" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H4" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H4" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I4" s="5" t="str"/>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -427,18 +440,21 @@
         <x:v>knowledge.fact</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H5" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H5" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I5" s="5" t="str"/>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
@@ -448,21 +464,24 @@
         <x:v>public.source_contract_evidence_manifests</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.evidence_manifest</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E6" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G6" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H6" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H6" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I6" s="5" t="str"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="str">
@@ -472,21 +491,24 @@
         <x:v>public.source_contract_evidence_metrics</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G7" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H7" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="str"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="5" t="str">
@@ -496,21 +518,24 @@
         <x:v>public.source_contract_evidence_rows</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.evidence_fragment_or_contract_fact_assertion</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E8" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F8" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G8" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H8" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H8" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I8" s="5" t="str"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="str">
@@ -520,21 +545,24 @@
         <x:v>public.source_contract_optimization_findings</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.contract_finding</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G9" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H9" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I9" s="5" t="str"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="5" t="str">
@@ -544,21 +572,24 @@
         <x:v>public.source_contract_optimization_levers</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.value_driver_or_commercial_lever</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F10" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G10" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H10" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I10" s="5" t="str"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="5" t="str">
@@ -568,21 +599,24 @@
         <x:v>public.source_contract_optimization_profiles</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.contract_profile</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G11" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H11" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H11" s="5" t="str"/>
+      <x:c r="I11" s="5" t="str"/>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="5" t="str">
@@ -595,18 +629,21 @@
         <x:v>knowledge.fact</x:v>
       </x:c>
       <x:c r="D12" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E12" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F12" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G12" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H12" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H12" s="5" t="str"/>
+      <x:c r="I12" s="5" t="str"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="5" t="str">
@@ -616,21 +653,24 @@
         <x:v>public.source_meeting_outcomes</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>unresolved</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F13" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G13" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H13" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H13" s="5" t="str"/>
+      <x:c r="I13" s="5" t="str"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="5" t="str">
@@ -640,21 +680,24 @@
         <x:v>public.source_value_chain</x:v>
       </x:c>
       <x:c r="C14" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.value_flow_step</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E14" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F14" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G14" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H14" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H14" s="5" t="str"/>
+      <x:c r="I14" s="5" t="str"/>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="5" t="str">
@@ -664,21 +707,24 @@
         <x:v>public.source_value_levers</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.value_driver_or_lever</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G15" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H15" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H15" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I15" s="5" t="str"/>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="5" t="str">
@@ -688,21 +734,24 @@
         <x:v>public.source_value_lines</x:v>
       </x:c>
       <x:c r="C16" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="D16" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>unresolved</x:v>
       </x:c>
       <x:c r="E16" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F16" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G16" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H16" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H16" s="5" t="str"/>
+      <x:c r="I16" s="5" t="str"/>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="5" t="str">
@@ -712,21 +761,24 @@
         <x:v>public.source_value_states</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.value_state_or_readiness</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E17" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F17" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G17" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H17" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H17" s="5" t="str"/>
+      <x:c r="I17" s="5" t="str"/>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="5" t="str">
@@ -736,21 +788,24 @@
         <x:v>public.source_vendor_commitments</x:v>
       </x:c>
       <x:c r="C18" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
+        <x:v>knowledge.commercial_commitment</x:v>
       </x:c>
       <x:c r="D18" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E18" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F18" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G18" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H18" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H18" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I18" s="5" t="str"/>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="5" t="str">
@@ -760,21 +815,24 @@
         <x:v>public.source_vendor_proposal_facts</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
+        <x:v>knowledge.proposal_fact_assertion</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E19" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F19" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G19" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H19" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H19" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I19" s="5" t="str"/>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="5" t="str">
@@ -784,21 +842,24 @@
         <x:v>public.vendor_contracts</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
+        <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E20" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F20" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G20" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H20" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H20" s="5" t="str">
+      <x:c r="I20" s="5" t="str">
         <x:v>Lineage field not found statically</x:v>
       </x:c>
     </x:row>
@@ -813,18 +874,21 @@
         <x:v>knowledge.metric_definition</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E21" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F21" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G21" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H21" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H21" s="5" t="str"/>
+      <x:c r="I21" s="5" t="str"/>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="5" t="str">
@@ -834,21 +898,24 @@
         <x:v>cio_tower.tool_identity_aliases</x:v>
       </x:c>
       <x:c r="C22" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="D22" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>unresolved</x:v>
       </x:c>
       <x:c r="E22" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F22" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G22" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H22" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H22" s="5" t="str"/>
+      <x:c r="I22" s="5" t="str"/>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="5" t="str">
@@ -858,21 +925,24 @@
         <x:v>public.ai_control_actions</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.action_or_decision</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E23" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F23" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G23" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H23" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H23" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I23" s="5" t="str"/>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="5" t="str">
@@ -882,21 +952,24 @@
         <x:v>public.ai_control_agent_outcomes</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.outcome</x:v>
       </x:c>
       <x:c r="D24" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E24" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F24" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G24" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H24" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H24" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I24" s="5" t="str"/>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="5" t="str">
@@ -906,21 +979,24 @@
         <x:v>public.ai_control_benefit_realization</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E25" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F25" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G25" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H25" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H25" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I25" s="5" t="str"/>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="5" t="str">
@@ -930,21 +1006,24 @@
         <x:v>public.ai_control_context_facts</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.fact_assertion</x:v>
       </x:c>
       <x:c r="D26" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E26" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F26" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G26" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H26" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H26" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I26" s="5" t="str"/>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="5" t="str">
@@ -954,21 +1033,24 @@
         <x:v>public.ai_control_context_relationships</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.relationship_assertion</x:v>
       </x:c>
       <x:c r="D27" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E27" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F27" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G27" s="5" t="str">
-        <x:v>High</x:v>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
       </x:c>
       <x:c r="H27" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I27" s="5" t="str">
         <x:v>Lineage field not found statically</x:v>
       </x:c>
     </x:row>
@@ -980,21 +1062,24 @@
         <x:v>public.ai_control_dora_metrics</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="D28" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E28" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F28" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G28" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H28" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H28" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I28" s="5" t="str"/>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="5" t="str">
@@ -1004,21 +1089,24 @@
         <x:v>public.ai_control_evidence_items</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E29" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F29" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G29" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H29" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H29" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I29" s="5" t="str"/>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="5" t="str">
@@ -1031,18 +1119,21 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="D30" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E30" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F30" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G30" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H30" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H30" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I30" s="5" t="str"/>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="5" t="str">
@@ -1052,21 +1143,24 @@
         <x:v>public.ai_control_persona_productivity</x:v>
       </x:c>
       <x:c r="C31" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="D31" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E31" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F31" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G31" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H31" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H31" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I31" s="5" t="str"/>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="5" t="str">
@@ -1079,18 +1173,21 @@
         <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="D32" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E32" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F32" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G32" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H32" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H32" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I32" s="5" t="str"/>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="5" t="str">
@@ -1103,18 +1200,21 @@
         <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="D33" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E33" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F33" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G33" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H33" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H33" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I33" s="5" t="str"/>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="5" t="str">
@@ -1124,21 +1224,24 @@
         <x:v>public.ai_control_tool_usage_monthly</x:v>
       </x:c>
       <x:c r="C34" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="D34" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E34" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F34" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G34" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H34" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H34" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I34" s="5" t="str"/>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="5" t="str">
@@ -1151,18 +1254,21 @@
         <x:v>knowledge.application</x:v>
       </x:c>
       <x:c r="D35" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E35" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F35" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G35" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H35" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H35" s="5" t="str">
+      <x:c r="I35" s="5" t="str">
         <x:v>Lineage field not found statically</x:v>
       </x:c>
     </x:row>
@@ -1174,21 +1280,24 @@
         <x:v>public.enterprise_context_records</x:v>
       </x:c>
       <x:c r="C36" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="D36" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>unresolved</x:v>
       </x:c>
       <x:c r="E36" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F36" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G36" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H36" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H36" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I36" s="5" t="str"/>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" s="5" t="str">
@@ -1201,18 +1310,21 @@
         <x:v>knowledge.application</x:v>
       </x:c>
       <x:c r="D37" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E37" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F37" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G37" s="5" t="str">
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H37" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="H37" s="5" t="str"/>
+      <x:c r="I37" s="5" t="str"/>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="5" t="str">
@@ -1225,18 +1337,21 @@
         <x:v>knowledge.vendor</x:v>
       </x:c>
       <x:c r="D38" s="5" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E38" s="5" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F38" s="5" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G38" s="5" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H38" s="5" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H38" s="5" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I38" s="5" t="str"/>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
       <x:c r="A39" s="6" t="str">
@@ -1249,18 +1364,21 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="D39" s="6" t="str">
-        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
+        <x:v>provisional</x:v>
       </x:c>
       <x:c r="E39" s="6" t="str">
-        <x:v>governance.object_identity_map</x:v>
+        <x:v>Approved/accepted/published state plus evidence lineage and tenant identity verified</x:v>
       </x:c>
       <x:c r="F39" s="6" t="str">
-        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+        <x:v>governance.object_identity_map</x:v>
       </x:c>
       <x:c r="G39" s="6" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="H39" s="6" t="str"/>
+        <x:v>source/evidence/provenance fields or outbox payload evidence</x:v>
+      </x:c>
+      <x:c r="H39" s="6" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I39" s="6" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
